--- a/ERP Carrier Name.XLSX
+++ b/ERP Carrier Name.XLSX
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://goodyearcorp-my.sharepoint.com/personal/julien_bechoux_goodyear_com/Documents/Desktop/AI/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://goodyearcorp-my.sharepoint.com/personal/julien_bechoux_goodyear_com/Documents/Desktop/AI/EMEA Freight Cost Tracker/JulienTest2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_AA821E43C4094E7AB64F0007AF3A5E031E853938" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50F7B7E6-C9BC-43C3-944E-9C2DE93D3DC6}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_C79EFD5AC4094E7AB64F0007AF843E01163FABEA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{662BE3A1-816B-4C95-83F3-033CE1BF7A98}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="2640" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1389" uniqueCount="1336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="1352">
   <si>
     <t>Brauch Transporte</t>
   </si>
@@ -3574,7 +3574,7 @@
     <t>Gerlach Customs Services LTD</t>
   </si>
   <si>
-    <t>MAERSK A/S (Sealand Europe A/S)</t>
+    <t>MAERSK A/S</t>
   </si>
   <si>
     <t>DeutschMann Internationale</t>
@@ -3631,6 +3631,9 @@
     <t>DSV Solutions srl</t>
   </si>
   <si>
+    <t>DHL Global Forwarding</t>
+  </si>
+  <si>
     <t>BDP INTERNATIONAL LOJISTIK LTD.STI.</t>
   </si>
   <si>
@@ -3982,12 +3985,24 @@
     <t>CEVA Logistics (U.A.E) - L.L.C</t>
   </si>
   <si>
+    <t>DHL Logistics Srl</t>
+  </si>
+  <si>
     <t>DHL Solutions k.s.</t>
   </si>
   <si>
+    <t>cargo-partner d.o.o.</t>
+  </si>
+  <si>
+    <t>EIMSKIP ISLAND EHF</t>
+  </si>
+  <si>
     <t>Raben Lietuva UAB</t>
   </si>
   <si>
+    <t>PSA BDP INTERNATIONAL LOJİSTİK</t>
+  </si>
+  <si>
     <t>Raben Logistics Czech s.r.o.</t>
   </si>
   <si>
@@ -4003,6 +4018,21 @@
     <t>Dan &amp; D Trans Plus Srl</t>
   </si>
   <si>
+    <t>Medlog France</t>
+  </si>
+  <si>
+    <t>Medlog NV</t>
+  </si>
+  <si>
+    <t>Medlog Spain Logistic SLU</t>
+  </si>
+  <si>
+    <t>Medlog Transport Poland SP.Z.O.O.</t>
+  </si>
+  <si>
+    <t>Medlog Lojistik Gemicilik Turizm A.</t>
+  </si>
+  <si>
     <t>Hans Ihro Gmbh</t>
   </si>
   <si>
@@ -4021,7 +4051,25 @@
     <t>QUALITAIR and SEA DIMOTRANS GROUP</t>
   </si>
   <si>
+    <t>OCEAN NETWORK EXPRESS SOUTH AFRICA</t>
+  </si>
+  <si>
+    <t>MAERSK SOUTH AFRICA (PTY) LTD</t>
+  </si>
+  <si>
     <t>DSV Air and Sea GmbH</t>
+  </si>
+  <si>
+    <t>Geis Tyre Solutions GmbH</t>
+  </si>
+  <si>
+    <t>MEDITERRANEAN SHIPPING COMPANY</t>
+  </si>
+  <si>
+    <t>Hapag-Lloyd Africa Pty Ltd</t>
+  </si>
+  <si>
+    <t>T-Mining NV</t>
   </si>
   <si>
     <t>Supplier</t>
@@ -4425,7 +4473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B1388"/>
+  <dimension ref="A1:B1405"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -4434,10 +4482,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>1334</v>
+        <v>1350</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1335</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -14450,7 +14498,7 @@
     </row>
     <row r="1253" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1253" s="2">
-        <v>90003323</v>
+        <v>90003279</v>
       </c>
       <c r="B1253" t="s">
         <v>1203</v>
@@ -14458,7 +14506,7 @@
     </row>
     <row r="1254" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1254" s="2">
-        <v>90003510</v>
+        <v>90003323</v>
       </c>
       <c r="B1254" t="s">
         <v>1204</v>
@@ -14466,7 +14514,7 @@
     </row>
     <row r="1255" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1255" s="2">
-        <v>90003511</v>
+        <v>90003510</v>
       </c>
       <c r="B1255" t="s">
         <v>1205</v>
@@ -14474,7 +14522,7 @@
     </row>
     <row r="1256" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1256" s="2">
-        <v>90003541</v>
+        <v>90003511</v>
       </c>
       <c r="B1256" t="s">
         <v>1206</v>
@@ -14482,7 +14530,7 @@
     </row>
     <row r="1257" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1257" s="2">
-        <v>90003542</v>
+        <v>90003541</v>
       </c>
       <c r="B1257" t="s">
         <v>1207</v>
@@ -14490,7 +14538,7 @@
     </row>
     <row r="1258" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1258" s="2">
-        <v>90003543</v>
+        <v>90003542</v>
       </c>
       <c r="B1258" t="s">
         <v>1208</v>
@@ -14498,7 +14546,7 @@
     </row>
     <row r="1259" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1259" s="2">
-        <v>90003621</v>
+        <v>90003543</v>
       </c>
       <c r="B1259" t="s">
         <v>1209</v>
@@ -14506,7 +14554,7 @@
     </row>
     <row r="1260" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1260" s="2">
-        <v>90003622</v>
+        <v>90003621</v>
       </c>
       <c r="B1260" t="s">
         <v>1210</v>
@@ -14514,7 +14562,7 @@
     </row>
     <row r="1261" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1261" s="2">
-        <v>90003779</v>
+        <v>90003622</v>
       </c>
       <c r="B1261" t="s">
         <v>1211</v>
@@ -14522,7 +14570,7 @@
     </row>
     <row r="1262" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1262" s="2">
-        <v>90003820</v>
+        <v>90003779</v>
       </c>
       <c r="B1262" t="s">
         <v>1212</v>
@@ -14530,7 +14578,7 @@
     </row>
     <row r="1263" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1263" s="2">
-        <v>90003821</v>
+        <v>90003820</v>
       </c>
       <c r="B1263" t="s">
         <v>1213</v>
@@ -14538,7 +14586,7 @@
     </row>
     <row r="1264" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1264" s="2">
-        <v>90003822</v>
+        <v>90003821</v>
       </c>
       <c r="B1264" t="s">
         <v>1214</v>
@@ -14546,7 +14594,7 @@
     </row>
     <row r="1265" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1265" s="2">
-        <v>90003823</v>
+        <v>90003822</v>
       </c>
       <c r="B1265" t="s">
         <v>1215</v>
@@ -14554,7 +14602,7 @@
     </row>
     <row r="1266" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1266" s="2">
-        <v>90003824</v>
+        <v>90003823</v>
       </c>
       <c r="B1266" t="s">
         <v>1216</v>
@@ -14562,7 +14610,7 @@
     </row>
     <row r="1267" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1267" s="2">
-        <v>90003825</v>
+        <v>90003824</v>
       </c>
       <c r="B1267" t="s">
         <v>1217</v>
@@ -14570,7 +14618,7 @@
     </row>
     <row r="1268" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1268" s="2">
-        <v>90003826</v>
+        <v>90003825</v>
       </c>
       <c r="B1268" t="s">
         <v>1218</v>
@@ -14578,7 +14626,7 @@
     </row>
     <row r="1269" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1269" s="2">
-        <v>90003827</v>
+        <v>90003826</v>
       </c>
       <c r="B1269" t="s">
         <v>1219</v>
@@ -14586,7 +14634,7 @@
     </row>
     <row r="1270" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1270" s="2">
-        <v>90003874</v>
+        <v>90003827</v>
       </c>
       <c r="B1270" t="s">
         <v>1220</v>
@@ -14594,23 +14642,23 @@
     </row>
     <row r="1271" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1271" s="2">
-        <v>90003875</v>
+        <v>90003874</v>
       </c>
       <c r="B1271" t="s">
-        <v>829</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="1272" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1272" s="2">
-        <v>90003876</v>
+        <v>90003875</v>
       </c>
       <c r="B1272" t="s">
-        <v>1221</v>
+        <v>829</v>
       </c>
     </row>
     <row r="1273" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1273" s="2">
-        <v>90003877</v>
+        <v>90003876</v>
       </c>
       <c r="B1273" t="s">
         <v>1222</v>
@@ -14618,7 +14666,7 @@
     </row>
     <row r="1274" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1274" s="2">
-        <v>90003895</v>
+        <v>90003877</v>
       </c>
       <c r="B1274" t="s">
         <v>1223</v>
@@ -14626,7 +14674,7 @@
     </row>
     <row r="1275" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1275" s="2">
-        <v>90004031</v>
+        <v>90003895</v>
       </c>
       <c r="B1275" t="s">
         <v>1224</v>
@@ -14634,7 +14682,7 @@
     </row>
     <row r="1276" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1276" s="2">
-        <v>90004064</v>
+        <v>90004031</v>
       </c>
       <c r="B1276" t="s">
         <v>1225</v>
@@ -14642,7 +14690,7 @@
     </row>
     <row r="1277" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1277" s="2">
-        <v>90004065</v>
+        <v>90004064</v>
       </c>
       <c r="B1277" t="s">
         <v>1226</v>
@@ -14650,7 +14698,7 @@
     </row>
     <row r="1278" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1278" s="2">
-        <v>90004066</v>
+        <v>90004065</v>
       </c>
       <c r="B1278" t="s">
         <v>1227</v>
@@ -14658,7 +14706,7 @@
     </row>
     <row r="1279" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1279" s="2">
-        <v>90004101</v>
+        <v>90004066</v>
       </c>
       <c r="B1279" t="s">
         <v>1228</v>
@@ -14666,7 +14714,7 @@
     </row>
     <row r="1280" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1280" s="2">
-        <v>90004102</v>
+        <v>90004101</v>
       </c>
       <c r="B1280" t="s">
         <v>1229</v>
@@ -14674,7 +14722,7 @@
     </row>
     <row r="1281" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1281" s="2">
-        <v>90004103</v>
+        <v>90004102</v>
       </c>
       <c r="B1281" t="s">
         <v>1230</v>
@@ -14682,7 +14730,7 @@
     </row>
     <row r="1282" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1282" s="2">
-        <v>90004209</v>
+        <v>90004103</v>
       </c>
       <c r="B1282" t="s">
         <v>1231</v>
@@ -14690,7 +14738,7 @@
     </row>
     <row r="1283" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1283" s="2">
-        <v>90004210</v>
+        <v>90004209</v>
       </c>
       <c r="B1283" t="s">
         <v>1232</v>
@@ -14698,7 +14746,7 @@
     </row>
     <row r="1284" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1284" s="2">
-        <v>90005761</v>
+        <v>90004210</v>
       </c>
       <c r="B1284" t="s">
         <v>1233</v>
@@ -14706,7 +14754,7 @@
     </row>
     <row r="1285" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1285" s="2">
-        <v>90005845</v>
+        <v>90005761</v>
       </c>
       <c r="B1285" t="s">
         <v>1234</v>
@@ -14714,7 +14762,7 @@
     </row>
     <row r="1286" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1286" s="2">
-        <v>90005846</v>
+        <v>90005845</v>
       </c>
       <c r="B1286" t="s">
         <v>1235</v>
@@ -14722,7 +14770,7 @@
     </row>
     <row r="1287" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1287" s="2">
-        <v>90005924</v>
+        <v>90005846</v>
       </c>
       <c r="B1287" t="s">
         <v>1236</v>
@@ -14730,7 +14778,7 @@
     </row>
     <row r="1288" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1288" s="2">
-        <v>90006023</v>
+        <v>90005924</v>
       </c>
       <c r="B1288" t="s">
         <v>1237</v>
@@ -14738,7 +14786,7 @@
     </row>
     <row r="1289" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1289" s="2">
-        <v>90006034</v>
+        <v>90006023</v>
       </c>
       <c r="B1289" t="s">
         <v>1238</v>
@@ -14746,7 +14794,7 @@
     </row>
     <row r="1290" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1290" s="2">
-        <v>90006060</v>
+        <v>90006034</v>
       </c>
       <c r="B1290" t="s">
         <v>1239</v>
@@ -14754,23 +14802,23 @@
     </row>
     <row r="1291" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1291" s="2">
-        <v>90006084</v>
+        <v>90006060</v>
       </c>
       <c r="B1291" t="s">
-        <v>1203</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="1292" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1292" s="2">
-        <v>90006126</v>
+        <v>90006084</v>
       </c>
       <c r="B1292" t="s">
-        <v>1240</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="1293" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1293" s="2">
-        <v>90006192</v>
+        <v>90006126</v>
       </c>
       <c r="B1293" t="s">
         <v>1241</v>
@@ -14778,7 +14826,7 @@
     </row>
     <row r="1294" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1294" s="2">
-        <v>90006242</v>
+        <v>90006192</v>
       </c>
       <c r="B1294" t="s">
         <v>1242</v>
@@ -14786,7 +14834,7 @@
     </row>
     <row r="1295" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1295" s="2">
-        <v>90006356</v>
+        <v>90006242</v>
       </c>
       <c r="B1295" t="s">
         <v>1243</v>
@@ -14794,7 +14842,7 @@
     </row>
     <row r="1296" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1296" s="2">
-        <v>90006357</v>
+        <v>90006356</v>
       </c>
       <c r="B1296" t="s">
         <v>1244</v>
@@ -14802,7 +14850,7 @@
     </row>
     <row r="1297" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1297" s="2">
-        <v>90006534</v>
+        <v>90006357</v>
       </c>
       <c r="B1297" t="s">
         <v>1245</v>
@@ -14810,7 +14858,7 @@
     </row>
     <row r="1298" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1298" s="2">
-        <v>90006535</v>
+        <v>90006534</v>
       </c>
       <c r="B1298" t="s">
         <v>1246</v>
@@ -14818,7 +14866,7 @@
     </row>
     <row r="1299" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1299" s="2">
-        <v>90006565</v>
+        <v>90006535</v>
       </c>
       <c r="B1299" t="s">
         <v>1247</v>
@@ -14826,7 +14874,7 @@
     </row>
     <row r="1300" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1300" s="2">
-        <v>90006583</v>
+        <v>90006565</v>
       </c>
       <c r="B1300" t="s">
         <v>1248</v>
@@ -14834,7 +14882,7 @@
     </row>
     <row r="1301" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1301" s="2">
-        <v>90006820</v>
+        <v>90006583</v>
       </c>
       <c r="B1301" t="s">
         <v>1249</v>
@@ -14842,7 +14890,7 @@
     </row>
     <row r="1302" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1302" s="2">
-        <v>90006849</v>
+        <v>90006820</v>
       </c>
       <c r="B1302" t="s">
         <v>1250</v>
@@ -14850,7 +14898,7 @@
     </row>
     <row r="1303" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1303" s="2">
-        <v>90006921</v>
+        <v>90006849</v>
       </c>
       <c r="B1303" t="s">
         <v>1251</v>
@@ -14858,7 +14906,7 @@
     </row>
     <row r="1304" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1304" s="2">
-        <v>90006926</v>
+        <v>90006921</v>
       </c>
       <c r="B1304" t="s">
         <v>1252</v>
@@ -14866,7 +14914,7 @@
     </row>
     <row r="1305" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1305" s="2">
-        <v>90006930</v>
+        <v>90006926</v>
       </c>
       <c r="B1305" t="s">
         <v>1253</v>
@@ -14874,7 +14922,7 @@
     </row>
     <row r="1306" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1306" s="2">
-        <v>90006980</v>
+        <v>90006930</v>
       </c>
       <c r="B1306" t="s">
         <v>1254</v>
@@ -14882,7 +14930,7 @@
     </row>
     <row r="1307" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1307" s="2">
-        <v>90007010</v>
+        <v>90006980</v>
       </c>
       <c r="B1307" t="s">
         <v>1255</v>
@@ -14890,7 +14938,7 @@
     </row>
     <row r="1308" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1308" s="2">
-        <v>90007086</v>
+        <v>90007010</v>
       </c>
       <c r="B1308" t="s">
         <v>1256</v>
@@ -14898,7 +14946,7 @@
     </row>
     <row r="1309" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1309" s="2">
-        <v>90007166</v>
+        <v>90007086</v>
       </c>
       <c r="B1309" t="s">
         <v>1257</v>
@@ -14906,7 +14954,7 @@
     </row>
     <row r="1310" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1310" s="2">
-        <v>90007242</v>
+        <v>90007166</v>
       </c>
       <c r="B1310" t="s">
         <v>1258</v>
@@ -14914,7 +14962,7 @@
     </row>
     <row r="1311" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1311" s="2">
-        <v>90007308</v>
+        <v>90007242</v>
       </c>
       <c r="B1311" t="s">
         <v>1259</v>
@@ -14922,7 +14970,7 @@
     </row>
     <row r="1312" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1312" s="2">
-        <v>90007330</v>
+        <v>90007308</v>
       </c>
       <c r="B1312" t="s">
         <v>1260</v>
@@ -14930,7 +14978,7 @@
     </row>
     <row r="1313" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1313" s="2">
-        <v>90007352</v>
+        <v>90007330</v>
       </c>
       <c r="B1313" t="s">
         <v>1261</v>
@@ -14938,7 +14986,7 @@
     </row>
     <row r="1314" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1314" s="2">
-        <v>90007382</v>
+        <v>90007352</v>
       </c>
       <c r="B1314" t="s">
         <v>1262</v>
@@ -14946,7 +14994,7 @@
     </row>
     <row r="1315" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1315" s="2">
-        <v>90007459</v>
+        <v>90007382</v>
       </c>
       <c r="B1315" t="s">
         <v>1263</v>
@@ -14954,7 +15002,7 @@
     </row>
     <row r="1316" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1316" s="2">
-        <v>90007480</v>
+        <v>90007459</v>
       </c>
       <c r="B1316" t="s">
         <v>1264</v>
@@ -14962,7 +15010,7 @@
     </row>
     <row r="1317" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1317" s="2">
-        <v>90007533</v>
+        <v>90007480</v>
       </c>
       <c r="B1317" t="s">
         <v>1265</v>
@@ -14970,7 +15018,7 @@
     </row>
     <row r="1318" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1318" s="2">
-        <v>90007534</v>
+        <v>90007533</v>
       </c>
       <c r="B1318" t="s">
         <v>1266</v>
@@ -14978,7 +15026,7 @@
     </row>
     <row r="1319" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1319" s="2">
-        <v>90007585</v>
+        <v>90007534</v>
       </c>
       <c r="B1319" t="s">
         <v>1267</v>
@@ -14986,7 +15034,7 @@
     </row>
     <row r="1320" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1320" s="2">
-        <v>90007605</v>
+        <v>90007585</v>
       </c>
       <c r="B1320" t="s">
         <v>1268</v>
@@ -14994,7 +15042,7 @@
     </row>
     <row r="1321" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1321" s="2">
-        <v>90007632</v>
+        <v>90007605</v>
       </c>
       <c r="B1321" t="s">
         <v>1269</v>
@@ -15002,7 +15050,7 @@
     </row>
     <row r="1322" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1322" s="2">
-        <v>90007718</v>
+        <v>90007632</v>
       </c>
       <c r="B1322" t="s">
         <v>1270</v>
@@ -15010,7 +15058,7 @@
     </row>
     <row r="1323" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1323" s="2">
-        <v>90007724</v>
+        <v>90007718</v>
       </c>
       <c r="B1323" t="s">
         <v>1271</v>
@@ -15018,7 +15066,7 @@
     </row>
     <row r="1324" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1324" s="2">
-        <v>90007743</v>
+        <v>90007724</v>
       </c>
       <c r="B1324" t="s">
         <v>1272</v>
@@ -15026,7 +15074,7 @@
     </row>
     <row r="1325" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1325" s="2">
-        <v>90007746</v>
+        <v>90007743</v>
       </c>
       <c r="B1325" t="s">
         <v>1273</v>
@@ -15034,7 +15082,7 @@
     </row>
     <row r="1326" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1326" s="2">
-        <v>90007751</v>
+        <v>90007746</v>
       </c>
       <c r="B1326" t="s">
         <v>1274</v>
@@ -15042,7 +15090,7 @@
     </row>
     <row r="1327" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1327" s="2">
-        <v>90007857</v>
+        <v>90007751</v>
       </c>
       <c r="B1327" t="s">
         <v>1275</v>
@@ -15050,23 +15098,23 @@
     </row>
     <row r="1328" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1328" s="2">
-        <v>90008000</v>
+        <v>90007857</v>
       </c>
       <c r="B1328" t="s">
-        <v>1258</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="1329" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1329" s="2">
-        <v>90008114</v>
+        <v>90008000</v>
       </c>
       <c r="B1329" t="s">
-        <v>1276</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="1330" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1330" s="2">
-        <v>90008320</v>
+        <v>90008114</v>
       </c>
       <c r="B1330" t="s">
         <v>1277</v>
@@ -15074,7 +15122,7 @@
     </row>
     <row r="1331" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1331" s="2">
-        <v>90008345</v>
+        <v>90008320</v>
       </c>
       <c r="B1331" t="s">
         <v>1278</v>
@@ -15082,7 +15130,7 @@
     </row>
     <row r="1332" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1332" s="2">
-        <v>90008403</v>
+        <v>90008345</v>
       </c>
       <c r="B1332" t="s">
         <v>1279</v>
@@ -15090,7 +15138,7 @@
     </row>
     <row r="1333" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1333" s="2">
-        <v>90008494</v>
+        <v>90008403</v>
       </c>
       <c r="B1333" t="s">
         <v>1280</v>
@@ -15098,7 +15146,7 @@
     </row>
     <row r="1334" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1334" s="2">
-        <v>90008570</v>
+        <v>90008494</v>
       </c>
       <c r="B1334" t="s">
         <v>1281</v>
@@ -15106,7 +15154,7 @@
     </row>
     <row r="1335" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1335" s="2">
-        <v>90008662</v>
+        <v>90008570</v>
       </c>
       <c r="B1335" t="s">
         <v>1282</v>
@@ -15114,7 +15162,7 @@
     </row>
     <row r="1336" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1336" s="2">
-        <v>90008873</v>
+        <v>90008662</v>
       </c>
       <c r="B1336" t="s">
         <v>1283</v>
@@ -15122,7 +15170,7 @@
     </row>
     <row r="1337" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1337" s="2">
-        <v>90009319</v>
+        <v>90008873</v>
       </c>
       <c r="B1337" t="s">
         <v>1284</v>
@@ -15130,7 +15178,7 @@
     </row>
     <row r="1338" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1338" s="2">
-        <v>90009339</v>
+        <v>90009319</v>
       </c>
       <c r="B1338" t="s">
         <v>1285</v>
@@ -15138,7 +15186,7 @@
     </row>
     <row r="1339" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1339" s="2">
-        <v>90009358</v>
+        <v>90009339</v>
       </c>
       <c r="B1339" t="s">
         <v>1286</v>
@@ -15146,7 +15194,7 @@
     </row>
     <row r="1340" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1340" s="2">
-        <v>90009387</v>
+        <v>90009358</v>
       </c>
       <c r="B1340" t="s">
         <v>1287</v>
@@ -15154,7 +15202,7 @@
     </row>
     <row r="1341" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1341" s="2">
-        <v>90009405</v>
+        <v>90009387</v>
       </c>
       <c r="B1341" t="s">
         <v>1288</v>
@@ -15162,7 +15210,7 @@
     </row>
     <row r="1342" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1342" s="2">
-        <v>90009432</v>
+        <v>90009405</v>
       </c>
       <c r="B1342" t="s">
         <v>1289</v>
@@ -15170,23 +15218,23 @@
     </row>
     <row r="1343" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1343" s="2">
-        <v>90009464</v>
+        <v>90009432</v>
       </c>
       <c r="B1343" t="s">
-        <v>1085</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="1344" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1344" s="2">
-        <v>90009483</v>
+        <v>90009464</v>
       </c>
       <c r="B1344" t="s">
-        <v>1290</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="1345" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1345" s="2">
-        <v>90009556</v>
+        <v>90009483</v>
       </c>
       <c r="B1345" t="s">
         <v>1291</v>
@@ -15194,7 +15242,7 @@
     </row>
     <row r="1346" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1346" s="2">
-        <v>90009563</v>
+        <v>90009556</v>
       </c>
       <c r="B1346" t="s">
         <v>1292</v>
@@ -15202,7 +15250,7 @@
     </row>
     <row r="1347" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1347" s="2">
-        <v>90009580</v>
+        <v>90009563</v>
       </c>
       <c r="B1347" t="s">
         <v>1293</v>
@@ -15210,7 +15258,7 @@
     </row>
     <row r="1348" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1348" s="2">
-        <v>90009581</v>
+        <v>90009580</v>
       </c>
       <c r="B1348" t="s">
         <v>1294</v>
@@ -15218,7 +15266,7 @@
     </row>
     <row r="1349" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1349" s="2">
-        <v>90009582</v>
+        <v>90009581</v>
       </c>
       <c r="B1349" t="s">
         <v>1295</v>
@@ -15226,7 +15274,7 @@
     </row>
     <row r="1350" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1350" s="2">
-        <v>90009680</v>
+        <v>90009582</v>
       </c>
       <c r="B1350" t="s">
         <v>1296</v>
@@ -15234,7 +15282,7 @@
     </row>
     <row r="1351" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1351" s="2">
-        <v>90009681</v>
+        <v>90009680</v>
       </c>
       <c r="B1351" t="s">
         <v>1297</v>
@@ -15242,7 +15290,7 @@
     </row>
     <row r="1352" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1352" s="2">
-        <v>90009682</v>
+        <v>90009681</v>
       </c>
       <c r="B1352" t="s">
         <v>1298</v>
@@ -15250,7 +15298,7 @@
     </row>
     <row r="1353" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1353" s="2">
-        <v>90009683</v>
+        <v>90009682</v>
       </c>
       <c r="B1353" t="s">
         <v>1299</v>
@@ -15258,7 +15306,7 @@
     </row>
     <row r="1354" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1354" s="2">
-        <v>90009684</v>
+        <v>90009683</v>
       </c>
       <c r="B1354" t="s">
         <v>1300</v>
@@ -15266,7 +15314,7 @@
     </row>
     <row r="1355" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1355" s="2">
-        <v>90009685</v>
+        <v>90009684</v>
       </c>
       <c r="B1355" t="s">
         <v>1301</v>
@@ -15274,7 +15322,7 @@
     </row>
     <row r="1356" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1356" s="2">
-        <v>90009714</v>
+        <v>90009685</v>
       </c>
       <c r="B1356" t="s">
         <v>1302</v>
@@ -15282,7 +15330,7 @@
     </row>
     <row r="1357" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1357" s="2">
-        <v>90009715</v>
+        <v>90009714</v>
       </c>
       <c r="B1357" t="s">
         <v>1303</v>
@@ -15290,7 +15338,7 @@
     </row>
     <row r="1358" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1358" s="2">
-        <v>90009719</v>
+        <v>90009715</v>
       </c>
       <c r="B1358" t="s">
         <v>1304</v>
@@ -15298,7 +15346,7 @@
     </row>
     <row r="1359" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1359" s="2">
-        <v>90009764</v>
+        <v>90009719</v>
       </c>
       <c r="B1359" t="s">
         <v>1305</v>
@@ -15306,7 +15354,7 @@
     </row>
     <row r="1360" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1360" s="2">
-        <v>90009796</v>
+        <v>90009764</v>
       </c>
       <c r="B1360" t="s">
         <v>1306</v>
@@ -15314,7 +15362,7 @@
     </row>
     <row r="1361" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1361" s="2">
-        <v>90009942</v>
+        <v>90009796</v>
       </c>
       <c r="B1361" t="s">
         <v>1307</v>
@@ -15322,7 +15370,7 @@
     </row>
     <row r="1362" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1362" s="2">
-        <v>90010132</v>
+        <v>90009942</v>
       </c>
       <c r="B1362" t="s">
         <v>1308</v>
@@ -15330,23 +15378,23 @@
     </row>
     <row r="1363" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1363" s="2">
-        <v>90010149</v>
+        <v>90010132</v>
       </c>
       <c r="B1363" t="s">
-        <v>853</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="1364" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1364" s="2">
-        <v>90010150</v>
+        <v>90010149</v>
       </c>
       <c r="B1364" t="s">
-        <v>1309</v>
+        <v>853</v>
       </c>
     </row>
     <row r="1365" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1365" s="2">
-        <v>90010392</v>
+        <v>90010150</v>
       </c>
       <c r="B1365" t="s">
         <v>1310</v>
@@ -15354,7 +15402,7 @@
     </row>
     <row r="1366" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1366" s="2">
-        <v>90010501</v>
+        <v>90010392</v>
       </c>
       <c r="B1366" t="s">
         <v>1311</v>
@@ -15362,7 +15410,7 @@
     </row>
     <row r="1367" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1367" s="2">
-        <v>90013173</v>
+        <v>90010501</v>
       </c>
       <c r="B1367" t="s">
         <v>1312</v>
@@ -15370,7 +15418,7 @@
     </row>
     <row r="1368" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1368" s="2">
-        <v>90014545</v>
+        <v>90013173</v>
       </c>
       <c r="B1368" t="s">
         <v>1313</v>
@@ -15378,7 +15426,7 @@
     </row>
     <row r="1369" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1369" s="2">
-        <v>90014677</v>
+        <v>90014545</v>
       </c>
       <c r="B1369" t="s">
         <v>1314</v>
@@ -15386,7 +15434,7 @@
     </row>
     <row r="1370" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1370" s="2">
-        <v>90015295</v>
+        <v>90014677</v>
       </c>
       <c r="B1370" t="s">
         <v>1315</v>
@@ -15394,7 +15442,7 @@
     </row>
     <row r="1371" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1371" s="2">
-        <v>90015578</v>
+        <v>90015295</v>
       </c>
       <c r="B1371" t="s">
         <v>1316</v>
@@ -15402,7 +15450,7 @@
     </row>
     <row r="1372" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1372" s="2">
-        <v>90016352</v>
+        <v>90015578</v>
       </c>
       <c r="B1372" t="s">
         <v>1317</v>
@@ -15410,7 +15458,7 @@
     </row>
     <row r="1373" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1373" s="2">
-        <v>90016441</v>
+        <v>90016352</v>
       </c>
       <c r="B1373" t="s">
         <v>1318</v>
@@ -15418,7 +15466,7 @@
     </row>
     <row r="1374" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1374" s="2">
-        <v>90017842</v>
+        <v>90016441</v>
       </c>
       <c r="B1374" t="s">
         <v>1319</v>
@@ -15426,7 +15474,7 @@
     </row>
     <row r="1375" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1375" s="2">
-        <v>90031616</v>
+        <v>90017842</v>
       </c>
       <c r="B1375" t="s">
         <v>1320</v>
@@ -15434,7 +15482,7 @@
     </row>
     <row r="1376" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1376" s="2">
-        <v>90036104</v>
+        <v>90018386</v>
       </c>
       <c r="B1376" t="s">
         <v>1321</v>
@@ -15442,7 +15490,7 @@
     </row>
     <row r="1377" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1377" s="2">
-        <v>90038066</v>
+        <v>90031616</v>
       </c>
       <c r="B1377" t="s">
         <v>1322</v>
@@ -15450,7 +15498,7 @@
     </row>
     <row r="1378" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1378" s="2">
-        <v>90038245</v>
+        <v>90031974</v>
       </c>
       <c r="B1378" t="s">
         <v>1323</v>
@@ -15458,7 +15506,7 @@
     </row>
     <row r="1379" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1379" s="2">
-        <v>90038454</v>
+        <v>90035311</v>
       </c>
       <c r="B1379" t="s">
         <v>1324</v>
@@ -15466,7 +15514,7 @@
     </row>
     <row r="1380" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1380" s="2">
-        <v>90038803</v>
+        <v>90036104</v>
       </c>
       <c r="B1380" t="s">
         <v>1325</v>
@@ -15474,7 +15522,7 @@
     </row>
     <row r="1381" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1381" s="2">
-        <v>90038804</v>
+        <v>90037642</v>
       </c>
       <c r="B1381" t="s">
         <v>1326</v>
@@ -15482,58 +15530,194 @@
     </row>
     <row r="1382" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1382" s="2">
-        <v>90039864</v>
+        <v>90037772</v>
       </c>
       <c r="B1382" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="1383" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1383" s="2">
-        <v>90040669</v>
+        <v>90038066</v>
       </c>
       <c r="B1383" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="1384" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1384" s="2">
-        <v>90040876</v>
+        <v>90038245</v>
       </c>
       <c r="B1384" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="1385" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1385" s="2">
-        <v>90041148</v>
+        <v>90038454</v>
       </c>
       <c r="B1385" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="1386" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1386" s="2">
-        <v>90041706</v>
+        <v>90038803</v>
       </c>
       <c r="B1386" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="1387" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1387" s="2">
-        <v>90041998</v>
+        <v>90038804</v>
       </c>
       <c r="B1387" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="1388" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1388" s="2">
+        <v>90039598</v>
+      </c>
+      <c r="B1388" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1389" s="2">
+        <v>90039624</v>
+      </c>
+      <c r="B1389" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1390" s="2">
+        <v>90039625</v>
+      </c>
+      <c r="B1390" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1391" s="2">
+        <v>90039626</v>
+      </c>
+      <c r="B1391" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1392" s="2">
+        <v>90039637</v>
+      </c>
+      <c r="B1392" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1393" s="2">
+        <v>90039864</v>
+      </c>
+      <c r="B1393" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1394" s="2">
+        <v>90040669</v>
+      </c>
+      <c r="B1394" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1395" s="2">
+        <v>90040876</v>
+      </c>
+      <c r="B1395" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1396" s="2">
+        <v>90041148</v>
+      </c>
+      <c r="B1396" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1397" s="2">
+        <v>90041706</v>
+      </c>
+      <c r="B1397" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1398" s="2">
+        <v>90041998</v>
+      </c>
+      <c r="B1398" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1399" s="2">
+        <v>90042061</v>
+      </c>
+      <c r="B1399" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1400" s="2">
+        <v>90042114</v>
+      </c>
+      <c r="B1400" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1401" s="2">
         <v>90042136</v>
       </c>
-      <c r="B1388" t="s">
-        <v>1333</v>
+      <c r="B1401" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1402" s="2">
+        <v>90042236</v>
+      </c>
+      <c r="B1402" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1403" s="2">
+        <v>90042369</v>
+      </c>
+      <c r="B1403" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1404" s="2">
+        <v>90042507</v>
+      </c>
+      <c r="B1404" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1405" s="2">
+        <v>90042549</v>
+      </c>
+      <c r="B1405" t="s">
+        <v>1349</v>
       </c>
     </row>
   </sheetData>

--- a/ERP Carrier Name.XLSX
+++ b/ERP Carrier Name.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://goodyearcorp-my.sharepoint.com/personal/julien_bechoux_goodyear_com/Documents/Desktop/AI/EMEA Freight Cost Tracker/JulienTest2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_C79EFD5AC4094E7AB64F0007AF843E01163FABEA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{274EAA3D-9379-4F0D-9333-C326CFD7F104}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_C79EFD5AC4094E7AB64F0007AF843E01163FABEA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4362DD5C-80B2-4389-A68F-E173E7206894}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4075,7 +4075,7 @@
     <t>ServcAgent</t>
   </si>
   <si>
-    <t>Carrier Name</t>
+    <t>Name 1</t>
   </si>
 </sst>
 </file>
